--- a/data/trans_dic/P64D1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D1_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,6; 36,39</t>
+          <t>24,68; 35,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,49; 37,3</t>
+          <t>28,3; 37,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,22; 35,41</t>
+          <t>27,78; 35,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 27,29</t>
+          <t>18,08; 27,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 37,13</t>
+          <t>28,12; 38,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,19; 30,49</t>
+          <t>24,1; 31,16</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 28,33</t>
+          <t>21,55; 33,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,13; 60,59</t>
+          <t>39,37; 59,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 33,38</t>
+          <t>26,81; 36,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 27,36</t>
+          <t>21,51; 29,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,8; 44,31</t>
+          <t>36,89; 44,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,01; 33,91</t>
+          <t>29,21; 34,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,76</t>
+          <t>12,75; 23,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,68; 70,73</t>
+          <t>33,95; 43,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,59; 53,23</t>
+          <t>24,1; 31,8</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,57; 24,31</t>
+          <t>22,64; 27,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,96; 49,32</t>
+          <t>35,28; 39,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 33,15</t>
+          <t>28,77; 31,99</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>114943</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209262</t>
+          <t>223369</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89804; 127642</t>
+          <t>94182; 134682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89071; 116591</t>
+          <t>94255; 123941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>187238; 234918</t>
+          <t>198550; 250574</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67196</t>
+          <t>72622</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>163249</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52744; 82775</t>
+          <t>57996; 88768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68515; 93607</t>
+          <t>76907; 104020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128805; 169356</t>
+          <t>143204; 185201</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100985</t>
+          <t>113580</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17164; 138677</t>
+          <t>58484; 90328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29382; 44359</t>
+          <t>32668; 49132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40843; 187821</t>
+          <t>95013; 131015</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>131733</t>
+          <t>157441</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>170748</t>
+          <t>194498</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302482</t>
+          <t>351939</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109647; 153141</t>
+          <t>133498; 181508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152673; 188982</t>
+          <t>176559; 214625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>276190; 334419</t>
+          <t>321123; 382442</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>53217</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174541</t>
+          <t>120480</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206623</t>
+          <t>173697</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21796; 47411</t>
+          <t>39127; 73228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118306; 264133</t>
+          <t>106267; 135854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144680; 326513</t>
+          <t>149415; 197122</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>402714</t>
+          <t>471254</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>564988</t>
+          <t>554579</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>967702</t>
+          <t>1025833</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>263757; 472345</t>
+          <t>430486; 515613</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>502690; 709202</t>
+          <t>522548; 588116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>777293; 1120868</t>
+          <t>973055; 1082168</t>
         </is>
       </c>
     </row>
